--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-12T22:27:00Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-13T22:31:31Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-13T22:31:31Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-14T23:16:42Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-14T23:16:42Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-15T23:01:38Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-15T23:01:38Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-16T23:07:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-16T23:07:47Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-17T17:37:54Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-17T17:37:54Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-17T22:58:09Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-17T22:58:09Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-18T22:43:52Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-18T22:43:52Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-19T22:23:11Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-19T22:23:11Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-20T22:35:40Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-20T22:35:40Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-21T23:27:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-21T23:27:46Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-22T17:38:13Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-22T17:38:13Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-22T23:08:01Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-22T23:08:01Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-23T23:02:37Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-23T23:02:37Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-24T23:17:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-24T23:17:56Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-25T23:23:38Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-25T23:23:38Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-26T23:03:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-26T23:03:46Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-27T23:13:00Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-27T23:13:00Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-29T00:28:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-29T00:28:21Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-29T23:51:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-29T23:51:56Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-01T00:02:18Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-01T00:02:18Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T00:01:22Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T00:01:22Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T18:24:22Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T18:24:22Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T23:55:29Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T23:55:29Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-03T23:14:12Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-03T23:14:12Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-04T23:25:17Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-04T23:25:17Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-06T01:22:20Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-06T01:22:20Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-06T23:56:58Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-06T23:56:58Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-07T19:19:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-07T19:19:47Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-08T00:18:14Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-08T00:18:14Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-09T00:32:02Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-09T00:32:02Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-10T00:11:24Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-10T00:11:24Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-10T23:42:24Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-10T23:42:24Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-11T23:49:13Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-11T23:49:13Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-12T21:43:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-12T21:43:47Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-13T02:10:27Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-13T02:10:27Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-13T23:48:06Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-13T23:48:06Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-14T23:20:55Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-14T23:20:55Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-15T23:09:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-15T23:09:48Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-16T22:56:26Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-16T22:56:26Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-17T16:23:40Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-17T16:23:40Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-17T22:30:19Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-17T22:30:19Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-18T22:31:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-18T22:31:21Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-19T23:50:39Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:39Z</t>
+          <t>2026-10-20T23:17:00Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-19T23:50:39Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-20T23:17:00Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:00Z</t>
+          <t>2026-10-21T23:30:20Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-20T23:17:00Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-21T23:30:20Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:20Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-21T23:30:20Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-22T17:58:31Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:28Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-22T17:58:31Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-22T23:29:28Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:28Z</t>
+          <t>2026-10-23T23:18:16Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-22T23:29:28Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-23T23:18:16Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:16Z</t>
+          <t>2026-10-24T22:37:21Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-23T23:18:16Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-24T22:37:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:21Z</t>
+          <t>2026-10-25T22:43:59Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-24T22:37:21Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-25T22:43:59Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:59Z</t>
+          <t>2026-10-26T23:58:53Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-25T22:43:59Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-26T23:58:53Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:53Z</t>
+          <t>2026-10-27T23:53:48Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-26T23:58:53Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-27T23:53:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:48Z</t>
+          <t>2026-10-29T00:09:56Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-27T23:53:48Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-29T00:09:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:56Z</t>
+          <t>2026-10-30T00:03:40Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-29T00:09:56Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-30T00:03:40Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:40Z</t>
+          <t>2026-10-30T23:56:21Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-30T00:03:40Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-30T23:56:21Z"}</t>
         </is>
       </c>
     </row>
